--- a/work/data/maturi_data.xlsx
+++ b/work/data/maturi_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BorisV\My Documents\dashboard\NEEBG\work\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF78A1E6-0164-49C7-ABB8-8499BDCAF823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3442A991-8CC9-4056-8DA0-AA6A177BCC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39AE1FD3-7C27-4CC1-AC71-0C6D056D2FEC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A348621D-5ED5-4FD9-8ED4-4EAC86F7337C}"/>
   </bookViews>
   <sheets>
     <sheet name="for_py2" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3714" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4244" uniqueCount="281">
   <si>
     <t>Година</t>
   </si>
@@ -875,6 +875,12 @@
   <si>
     <t>2018-2019</t>
   </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>ГР.ДОБРИЧ</t>
+  </si>
 </sst>
 </file>
 
@@ -1224,8 +1230,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B54EDBD-BD97-4AB9-B2C9-C36806C01ED7}">
-  <dimension ref="A1:F1855"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC979185-D86E-4BF3-A367-64AA1AD3F698}">
+  <dimension ref="A1:F2120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -38339,6 +38345,5306 @@
         <v>656</v>
       </c>
     </row>
+    <row r="1856" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1856" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1856">
+        <v>33.73985294117648</v>
+      </c>
+      <c r="D1856">
+        <v>136</v>
+      </c>
+      <c r="E1856">
+        <v>16.148208955223883</v>
+      </c>
+      <c r="F1856">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1857" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1857">
+        <v>44.171886792452824</v>
+      </c>
+      <c r="D1857">
+        <v>53</v>
+      </c>
+      <c r="E1857">
+        <v>22.056037735849056</v>
+      </c>
+      <c r="F1857">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1858" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1858">
+        <v>45.963300970873782</v>
+      </c>
+      <c r="D1858">
+        <v>206</v>
+      </c>
+      <c r="E1858">
+        <v>32.395658536585358</v>
+      </c>
+      <c r="F1858">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1859" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1859">
+        <v>43.215661764705885</v>
+      </c>
+      <c r="D1859">
+        <v>136</v>
+      </c>
+      <c r="E1859">
+        <v>24.666148148148149</v>
+      </c>
+      <c r="F1859">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1860" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1860">
+        <v>19</v>
+      </c>
+      <c r="D1860">
+        <v>10</v>
+      </c>
+      <c r="E1860">
+        <v>14.25</v>
+      </c>
+      <c r="F1860">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1861" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1861">
+        <v>28.08</v>
+      </c>
+      <c r="D1861">
+        <v>6</v>
+      </c>
+      <c r="E1861">
+        <v>13.679999999999998</v>
+      </c>
+      <c r="F1861">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1862" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1862">
+        <v>40.544090909090912</v>
+      </c>
+      <c r="D1862">
+        <v>22</v>
+      </c>
+      <c r="E1862">
+        <v>35.593636363636364</v>
+      </c>
+      <c r="F1862">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1863" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1863">
+        <v>52.47</v>
+      </c>
+      <c r="D1863">
+        <v>17</v>
+      </c>
+      <c r="E1863">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="F1863">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1864" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1864">
+        <v>56.074814814814815</v>
+      </c>
+      <c r="D1864">
+        <v>27</v>
+      </c>
+      <c r="E1864">
+        <v>35.824074074074076</v>
+      </c>
+      <c r="F1864">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1865" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1865">
+        <v>51.687870563674316</v>
+      </c>
+      <c r="D1865">
+        <v>479</v>
+      </c>
+      <c r="E1865">
+        <v>33.197411273486431</v>
+      </c>
+      <c r="F1865">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1866" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1866">
+        <v>47.138041237113406</v>
+      </c>
+      <c r="D1866">
+        <v>97</v>
+      </c>
+      <c r="E1866">
+        <v>28.103838383838383</v>
+      </c>
+      <c r="F1866">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1867" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1867">
+        <v>68.372500000000002</v>
+      </c>
+      <c r="D1867">
+        <v>16</v>
+      </c>
+      <c r="E1867">
+        <v>64.55</v>
+      </c>
+      <c r="F1867">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1868" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1868">
+        <v>55.228571428571428</v>
+      </c>
+      <c r="D1868">
+        <v>98</v>
+      </c>
+      <c r="E1868">
+        <v>32.427142857142861</v>
+      </c>
+      <c r="F1868">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1869" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1869">
+        <v>55.064545454545453</v>
+      </c>
+      <c r="D1869">
+        <v>33</v>
+      </c>
+      <c r="E1869">
+        <v>31.242121212121212</v>
+      </c>
+      <c r="F1869">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1870" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1870">
+        <v>52.834594594594599</v>
+      </c>
+      <c r="D1870">
+        <v>37</v>
+      </c>
+      <c r="E1870">
+        <v>30.048108108108107</v>
+      </c>
+      <c r="F1870">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1871" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1871">
+        <v>54.412560975609757</v>
+      </c>
+      <c r="D1871">
+        <v>82</v>
+      </c>
+      <c r="E1871">
+        <v>43.559876543209882</v>
+      </c>
+      <c r="F1871">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1872" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1872" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1872">
+        <v>42.899387755102047</v>
+      </c>
+      <c r="D1872">
+        <v>49</v>
+      </c>
+      <c r="E1872">
+        <v>23.613958333333333</v>
+      </c>
+      <c r="F1872">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1873" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1873" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1873">
+        <v>26.665294117647058</v>
+      </c>
+      <c r="D1873">
+        <v>34</v>
+      </c>
+      <c r="E1873">
+        <v>14.409999999999998</v>
+      </c>
+      <c r="F1873">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1874" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1874">
+        <v>48.817887323943658</v>
+      </c>
+      <c r="D1874">
+        <v>71</v>
+      </c>
+      <c r="E1874">
+        <v>29.513043478260872</v>
+      </c>
+      <c r="F1874">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1875" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1875" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1875">
+        <v>42.863185840707963</v>
+      </c>
+      <c r="D1875">
+        <v>113</v>
+      </c>
+      <c r="E1875">
+        <v>23.536339285714288</v>
+      </c>
+      <c r="F1875">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1876" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1876" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1876">
+        <v>66.919035769828923</v>
+      </c>
+      <c r="D1876">
+        <v>643</v>
+      </c>
+      <c r="E1876">
+        <v>45.767004680187213</v>
+      </c>
+      <c r="F1876">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1877" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1877" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1877">
+        <v>35.245517241379318</v>
+      </c>
+      <c r="D1877">
+        <v>29</v>
+      </c>
+      <c r="E1877">
+        <v>18.813703703703702</v>
+      </c>
+      <c r="F1877">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1878" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1878" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1878">
+        <v>59.330000000000005</v>
+      </c>
+      <c r="D1878">
+        <v>6</v>
+      </c>
+      <c r="E1878">
+        <v>37.92</v>
+      </c>
+      <c r="F1878">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1879" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1879" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1879">
+        <v>59.499176470588239</v>
+      </c>
+      <c r="D1879">
+        <v>85</v>
+      </c>
+      <c r="E1879">
+        <v>35.820823529411761</v>
+      </c>
+      <c r="F1879">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1880" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1880" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1880">
+        <v>23.5</v>
+      </c>
+      <c r="D1880">
+        <v>3</v>
+      </c>
+      <c r="E1880">
+        <v>24.25</v>
+      </c>
+      <c r="F1880">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1881" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1881" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1881">
+        <v>41.972000000000001</v>
+      </c>
+      <c r="D1881">
+        <v>50</v>
+      </c>
+      <c r="E1881">
+        <v>16.233400000000003</v>
+      </c>
+      <c r="F1881">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1882" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1882" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1882">
+        <v>33.037692307692311</v>
+      </c>
+      <c r="D1882">
+        <v>13</v>
+      </c>
+      <c r="E1882">
+        <v>26.546000000000003</v>
+      </c>
+      <c r="F1882">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1883" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1883" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1883">
+        <v>53.167777777777779</v>
+      </c>
+      <c r="D1883">
+        <v>9</v>
+      </c>
+      <c r="E1883">
+        <v>39.442222222222227</v>
+      </c>
+      <c r="F1883">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1884" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1884" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1884">
+        <v>32.835306122448976</v>
+      </c>
+      <c r="D1884">
+        <v>49</v>
+      </c>
+      <c r="E1884">
+        <v>14.714897959183673</v>
+      </c>
+      <c r="F1884">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1885" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1885" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1885">
+        <v>28.716250000000002</v>
+      </c>
+      <c r="D1885">
+        <v>16</v>
+      </c>
+      <c r="E1885">
+        <v>26.471874999999997</v>
+      </c>
+      <c r="F1885">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1886" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1886" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1886">
+        <v>57.956976744186036</v>
+      </c>
+      <c r="D1886">
+        <v>258</v>
+      </c>
+      <c r="E1886">
+        <v>35.223281249999999</v>
+      </c>
+      <c r="F1886">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1887" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1887" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1887">
+        <v>30.737368421052633</v>
+      </c>
+      <c r="D1887">
+        <v>38</v>
+      </c>
+      <c r="E1887">
+        <v>27.231025641025642</v>
+      </c>
+      <c r="F1887">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1888" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1888" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1888">
+        <v>28.20882352941177</v>
+      </c>
+      <c r="D1888">
+        <v>34</v>
+      </c>
+      <c r="E1888">
+        <v>16.240588235294119</v>
+      </c>
+      <c r="F1888">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1889" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1889" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1889">
+        <v>28.06</v>
+      </c>
+      <c r="D1889">
+        <v>8</v>
+      </c>
+      <c r="E1889">
+        <v>13</v>
+      </c>
+      <c r="F1889">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1890" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1890">
+        <v>60.1871875</v>
+      </c>
+      <c r="D1890">
+        <v>32</v>
+      </c>
+      <c r="E1890">
+        <v>30.142580645161289</v>
+      </c>
+      <c r="F1890">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1891" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1891">
+        <v>25.52921052631579</v>
+      </c>
+      <c r="D1891">
+        <v>38</v>
+      </c>
+      <c r="E1891">
+        <v>15.314736842105264</v>
+      </c>
+      <c r="F1891">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1892" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1892">
+        <v>35.586785714285718</v>
+      </c>
+      <c r="D1892">
+        <v>28</v>
+      </c>
+      <c r="E1892">
+        <v>22.379259259259261</v>
+      </c>
+      <c r="F1892">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1893" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1893">
+        <v>62.015534907081864</v>
+      </c>
+      <c r="D1893">
+        <v>1991</v>
+      </c>
+      <c r="E1893">
+        <v>47.206590909090906</v>
+      </c>
+      <c r="F1893">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1894" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1894">
+        <v>41.124489795918365</v>
+      </c>
+      <c r="D1894">
+        <v>98</v>
+      </c>
+      <c r="E1894">
+        <v>20.350918367346939</v>
+      </c>
+      <c r="F1894">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1895" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1895">
+        <v>37.130773195876287</v>
+      </c>
+      <c r="D1895">
+        <v>194</v>
+      </c>
+      <c r="E1895">
+        <v>16.693333333333332</v>
+      </c>
+      <c r="F1895">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1896" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1896">
+        <v>66.793164928292029</v>
+      </c>
+      <c r="D1896">
+        <v>3068</v>
+      </c>
+      <c r="E1896">
+        <v>52.881851730894837</v>
+      </c>
+      <c r="F1896">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1897" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1897">
+        <v>40.110980392156861</v>
+      </c>
+      <c r="D1897">
+        <v>51</v>
+      </c>
+      <c r="E1897">
+        <v>23.04673076923077</v>
+      </c>
+      <c r="F1897">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1898" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1898">
+        <v>61.821571815718144</v>
+      </c>
+      <c r="D1898">
+        <v>738</v>
+      </c>
+      <c r="E1898">
+        <v>45.232279511533243</v>
+      </c>
+      <c r="F1898">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1899" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1899">
+        <v>49.75610108303249</v>
+      </c>
+      <c r="D1899">
+        <v>277</v>
+      </c>
+      <c r="E1899">
+        <v>31.98723636363637</v>
+      </c>
+      <c r="F1899">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1900" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1900">
+        <v>24.540882352941175</v>
+      </c>
+      <c r="D1900">
+        <v>34</v>
+      </c>
+      <c r="E1900">
+        <v>23.242058823529412</v>
+      </c>
+      <c r="F1900">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1901" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1901">
+        <v>32.098923076923072</v>
+      </c>
+      <c r="D1901">
+        <v>65</v>
+      </c>
+      <c r="E1901">
+        <v>19.364516129032257</v>
+      </c>
+      <c r="F1901">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1902" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1902">
+        <v>34.78</v>
+      </c>
+      <c r="D1902">
+        <v>23</v>
+      </c>
+      <c r="E1902">
+        <v>17.66</v>
+      </c>
+      <c r="F1902">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1903" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1903">
+        <v>51.994649859943976</v>
+      </c>
+      <c r="D1903">
+        <v>357</v>
+      </c>
+      <c r="E1903">
+        <v>29.599803921568629</v>
+      </c>
+      <c r="F1903">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1904" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1904">
+        <v>62.409959432048673</v>
+      </c>
+      <c r="D1904">
+        <v>493</v>
+      </c>
+      <c r="E1904">
+        <v>34.865184426229504</v>
+      </c>
+      <c r="F1904">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1905" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1905">
+        <v>31.50928571428571</v>
+      </c>
+      <c r="D1905">
+        <v>56</v>
+      </c>
+      <c r="E1905">
+        <v>13.215357142857142</v>
+      </c>
+      <c r="F1905">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1906" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1906">
+        <v>28.92257575757576</v>
+      </c>
+      <c r="D1906">
+        <v>66</v>
+      </c>
+      <c r="E1906">
+        <v>17.306363636363635</v>
+      </c>
+      <c r="F1906">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1907" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1907">
+        <v>36.092711864406787</v>
+      </c>
+      <c r="D1907">
+        <v>59</v>
+      </c>
+      <c r="E1907">
+        <v>18.175423728813559</v>
+      </c>
+      <c r="F1907">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1908" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1908">
+        <v>27.44</v>
+      </c>
+      <c r="D1908">
+        <v>39</v>
+      </c>
+      <c r="E1908">
+        <v>16.95</v>
+      </c>
+      <c r="F1908">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1909" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1909">
+        <v>60.865318066157762</v>
+      </c>
+      <c r="D1909">
+        <v>393</v>
+      </c>
+      <c r="E1909">
+        <v>38.621020408163261</v>
+      </c>
+      <c r="F1909">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1910" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1910">
+        <v>33.799285714285709</v>
+      </c>
+      <c r="D1910">
+        <v>70</v>
+      </c>
+      <c r="E1910">
+        <v>17.801285714285715</v>
+      </c>
+      <c r="F1910">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1911" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1911">
+        <v>48.669999999999995</v>
+      </c>
+      <c r="D1911">
+        <v>6</v>
+      </c>
+      <c r="E1911">
+        <v>21.790000000000003</v>
+      </c>
+      <c r="F1911">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1912" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1912">
+        <v>36.970526315789478</v>
+      </c>
+      <c r="D1912">
+        <v>38</v>
+      </c>
+      <c r="E1912">
+        <v>24.419166666666669</v>
+      </c>
+      <c r="F1912">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1913" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1913">
+        <v>43.7</v>
+      </c>
+      <c r="D1913">
+        <v>23</v>
+      </c>
+      <c r="E1913">
+        <v>23.1</v>
+      </c>
+      <c r="F1913">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1914" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1914">
+        <v>48.671607142857148</v>
+      </c>
+      <c r="D1914">
+        <v>56</v>
+      </c>
+      <c r="E1914">
+        <v>29.212631578947367</v>
+      </c>
+      <c r="F1914">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1915" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1915">
+        <v>56.130899280575541</v>
+      </c>
+      <c r="D1915">
+        <v>278</v>
+      </c>
+      <c r="E1915">
+        <v>33.558545454545452</v>
+      </c>
+      <c r="F1915">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1916" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1916">
+        <v>60.115619047619056</v>
+      </c>
+      <c r="D1916">
+        <v>315</v>
+      </c>
+      <c r="E1916">
+        <v>33.069012738853502</v>
+      </c>
+      <c r="F1916">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1917" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1917">
+        <v>59.204564102564099</v>
+      </c>
+      <c r="D1917">
+        <v>585</v>
+      </c>
+      <c r="E1917">
+        <v>41.057247863247859</v>
+      </c>
+      <c r="F1917">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1918" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1918">
+        <v>22.6</v>
+      </c>
+      <c r="D1918">
+        <v>5</v>
+      </c>
+      <c r="E1918">
+        <v>11.88</v>
+      </c>
+      <c r="F1918">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1919" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1919">
+        <v>42.57261904761905</v>
+      </c>
+      <c r="D1919">
+        <v>42</v>
+      </c>
+      <c r="E1919">
+        <v>29.637142857142855</v>
+      </c>
+      <c r="F1919">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1920" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1920">
+        <v>31.543636363636367</v>
+      </c>
+      <c r="D1920">
+        <v>44</v>
+      </c>
+      <c r="E1920">
+        <v>16.90285714285714</v>
+      </c>
+      <c r="F1920">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1921" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1921">
+        <v>32.154367816091955</v>
+      </c>
+      <c r="D1921">
+        <v>87</v>
+      </c>
+      <c r="E1921">
+        <v>16.973139534883721</v>
+      </c>
+      <c r="F1921">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1922" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1922">
+        <v>42.422191780821919</v>
+      </c>
+      <c r="D1922">
+        <v>146</v>
+      </c>
+      <c r="E1922">
+        <v>31.551258741258746</v>
+      </c>
+      <c r="F1922">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1923" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1923">
+        <v>39.656923076923078</v>
+      </c>
+      <c r="D1923">
+        <v>39</v>
+      </c>
+      <c r="E1923">
+        <v>16.801052631578944</v>
+      </c>
+      <c r="F1923">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1924" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1924">
+        <v>55.11666666666666</v>
+      </c>
+      <c r="D1924">
+        <v>51</v>
+      </c>
+      <c r="E1924">
+        <v>33.368627450980398</v>
+      </c>
+      <c r="F1924">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1925" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1925">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D1925">
+        <v>56</v>
+      </c>
+      <c r="E1925">
+        <v>18.03</v>
+      </c>
+      <c r="F1925">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1926" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1926">
+        <v>49.542285714285718</v>
+      </c>
+      <c r="D1926">
+        <v>35</v>
+      </c>
+      <c r="E1926">
+        <v>38.610857142857149</v>
+      </c>
+      <c r="F1926">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1927" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1927">
+        <v>45.274837758112092</v>
+      </c>
+      <c r="D1927">
+        <v>339</v>
+      </c>
+      <c r="E1927">
+        <v>26.642064896755155</v>
+      </c>
+      <c r="F1927">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1928" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1928">
+        <v>27.704545454545453</v>
+      </c>
+      <c r="D1928">
+        <v>22</v>
+      </c>
+      <c r="E1928">
+        <v>14.158181818181818</v>
+      </c>
+      <c r="F1928">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1929" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1929">
+        <v>26.128620689655168</v>
+      </c>
+      <c r="D1929">
+        <v>87</v>
+      </c>
+      <c r="E1929">
+        <v>16.173023255813956</v>
+      </c>
+      <c r="F1929">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1930" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1930">
+        <v>39.57</v>
+      </c>
+      <c r="D1930">
+        <v>34</v>
+      </c>
+      <c r="E1930">
+        <v>28.23</v>
+      </c>
+      <c r="F1930">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1931" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1931">
+        <v>36.139493670886075</v>
+      </c>
+      <c r="D1931">
+        <v>79</v>
+      </c>
+      <c r="E1931">
+        <v>17.611410256410256</v>
+      </c>
+      <c r="F1931">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1932" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1932">
+        <v>35.547647058823529</v>
+      </c>
+      <c r="D1932">
+        <v>51</v>
+      </c>
+      <c r="E1932">
+        <v>27.724897959183672</v>
+      </c>
+      <c r="F1932">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1933" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1933">
+        <v>30.845564516129031</v>
+      </c>
+      <c r="D1933">
+        <v>124</v>
+      </c>
+      <c r="E1933">
+        <v>19.077073170731708</v>
+      </c>
+      <c r="F1933">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1934" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1934">
+        <v>63.29490566037736</v>
+      </c>
+      <c r="D1934">
+        <v>53</v>
+      </c>
+      <c r="E1934">
+        <v>54.276037735849059</v>
+      </c>
+      <c r="F1934">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1935" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1935">
+        <v>49.71</v>
+      </c>
+      <c r="D1935">
+        <v>19</v>
+      </c>
+      <c r="E1935">
+        <v>21.55</v>
+      </c>
+      <c r="F1935">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1936" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1936">
+        <v>40.56</v>
+      </c>
+      <c r="D1936">
+        <v>36</v>
+      </c>
+      <c r="E1936">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="F1936">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1937" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1937">
+        <v>37.604482758620691</v>
+      </c>
+      <c r="D1937">
+        <v>203</v>
+      </c>
+      <c r="E1937">
+        <v>32.784656862745095</v>
+      </c>
+      <c r="F1937">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1938" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1938">
+        <v>55.931249999999991</v>
+      </c>
+      <c r="D1938">
+        <v>296</v>
+      </c>
+      <c r="E1938">
+        <v>35.156836734693883</v>
+      </c>
+      <c r="F1938">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1939" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1939">
+        <v>30.379325842696627</v>
+      </c>
+      <c r="D1939">
+        <v>89</v>
+      </c>
+      <c r="E1939">
+        <v>17.021348314606744</v>
+      </c>
+      <c r="F1939">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1940" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1940">
+        <v>43.548039215686273</v>
+      </c>
+      <c r="D1940">
+        <v>51</v>
+      </c>
+      <c r="E1940">
+        <v>25.440980392156863</v>
+      </c>
+      <c r="F1940">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1941" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1941">
+        <v>57.980999999999995</v>
+      </c>
+      <c r="D1941">
+        <v>160</v>
+      </c>
+      <c r="E1941">
+        <v>35.270691823899369</v>
+      </c>
+      <c r="F1941">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1942" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1942">
+        <v>31.988876404494384</v>
+      </c>
+      <c r="D1942">
+        <v>89</v>
+      </c>
+      <c r="E1942">
+        <v>19.134555555555558</v>
+      </c>
+      <c r="F1942">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1943" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1943">
+        <v>44.119069767441857</v>
+      </c>
+      <c r="D1943">
+        <v>86</v>
+      </c>
+      <c r="E1943">
+        <v>26.461744186046513</v>
+      </c>
+      <c r="F1943">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1944" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1944">
+        <v>41.866756756756764</v>
+      </c>
+      <c r="D1944">
+        <v>37</v>
+      </c>
+      <c r="E1944">
+        <v>29.897837837837837</v>
+      </c>
+      <c r="F1944">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1945" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1945">
+        <v>44.8</v>
+      </c>
+      <c r="D1945">
+        <v>10</v>
+      </c>
+      <c r="E1945">
+        <v>21</v>
+      </c>
+      <c r="F1945">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1946" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1946">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="D1946">
+        <v>23</v>
+      </c>
+      <c r="E1946">
+        <v>11.116521739130434</v>
+      </c>
+      <c r="F1946">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1947" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1947">
+        <v>53.01</v>
+      </c>
+      <c r="D1947">
+        <v>44</v>
+      </c>
+      <c r="E1947">
+        <v>25.87</v>
+      </c>
+      <c r="F1947">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1948" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1948">
+        <v>64.949285714285722</v>
+      </c>
+      <c r="D1948">
+        <v>56</v>
+      </c>
+      <c r="E1948">
+        <v>44.70446428571428</v>
+      </c>
+      <c r="F1948">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1949" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1949">
+        <v>55.920277777777777</v>
+      </c>
+      <c r="D1949">
+        <v>36</v>
+      </c>
+      <c r="E1949">
+        <v>43.61</v>
+      </c>
+      <c r="F1949">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1950" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1950">
+        <v>46.808095238095241</v>
+      </c>
+      <c r="D1950">
+        <v>21</v>
+      </c>
+      <c r="E1950">
+        <v>23.640952380952381</v>
+      </c>
+      <c r="F1950">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1951" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1951">
+        <v>33.63219512195122</v>
+      </c>
+      <c r="D1951">
+        <v>41</v>
+      </c>
+      <c r="E1951">
+        <v>13.47609756097561</v>
+      </c>
+      <c r="F1951">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1952" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1952">
+        <v>39.704071856287428</v>
+      </c>
+      <c r="D1952">
+        <v>167</v>
+      </c>
+      <c r="E1952">
+        <v>27.500180722891571</v>
+      </c>
+      <c r="F1952">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1953" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1953">
+        <v>30.809404761904759</v>
+      </c>
+      <c r="D1953">
+        <v>168</v>
+      </c>
+      <c r="E1953">
+        <v>19.397261904761905</v>
+      </c>
+      <c r="F1953">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1954" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1954">
+        <v>44.748219178082188</v>
+      </c>
+      <c r="D1954">
+        <v>73</v>
+      </c>
+      <c r="E1954">
+        <v>28.969041095890407</v>
+      </c>
+      <c r="F1954">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1955" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1955">
+        <v>52.145119453924913</v>
+      </c>
+      <c r="D1955">
+        <v>586</v>
+      </c>
+      <c r="E1955">
+        <v>33.167969283276449</v>
+      </c>
+      <c r="F1955">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1956" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1956">
+        <v>22.331428571428571</v>
+      </c>
+      <c r="D1956">
+        <v>35</v>
+      </c>
+      <c r="E1956">
+        <v>14.316176470588236</v>
+      </c>
+      <c r="F1956">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1957" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1957">
+        <v>40.659999999999997</v>
+      </c>
+      <c r="D1957">
+        <v>63</v>
+      </c>
+      <c r="E1957">
+        <v>24.139218749999998</v>
+      </c>
+      <c r="F1957">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1958" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1958">
+        <v>41.156315789473688</v>
+      </c>
+      <c r="D1958">
+        <v>38</v>
+      </c>
+      <c r="E1958">
+        <v>25.603157894736842</v>
+      </c>
+      <c r="F1958">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1959" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1959">
+        <v>21.84154639175258</v>
+      </c>
+      <c r="D1959">
+        <v>97</v>
+      </c>
+      <c r="E1959">
+        <v>19.252783505154639</v>
+      </c>
+      <c r="F1959">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1960" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1960">
+        <v>44.087322274881515</v>
+      </c>
+      <c r="D1960">
+        <v>422</v>
+      </c>
+      <c r="E1960">
+        <v>28.432033898305086</v>
+      </c>
+      <c r="F1960">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1961" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1961">
+        <v>49.40904255319149</v>
+      </c>
+      <c r="D1961">
+        <v>188</v>
+      </c>
+      <c r="E1961">
+        <v>47.832688172043007</v>
+      </c>
+      <c r="F1961">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1962" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1962">
+        <v>27.509375000000002</v>
+      </c>
+      <c r="D1962">
+        <v>48</v>
+      </c>
+      <c r="E1962">
+        <v>13.563617021276595</v>
+      </c>
+      <c r="F1962">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1963" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1963">
+        <v>45.435779816513758</v>
+      </c>
+      <c r="D1963">
+        <v>109</v>
+      </c>
+      <c r="E1963">
+        <v>38.117592592592594</v>
+      </c>
+      <c r="F1963">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1964" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1964">
+        <v>37.974204545454548</v>
+      </c>
+      <c r="D1964">
+        <v>88</v>
+      </c>
+      <c r="E1964">
+        <v>29.934269662921345</v>
+      </c>
+      <c r="F1964">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1965" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1965">
+        <v>40.33</v>
+      </c>
+      <c r="D1965">
+        <v>3</v>
+      </c>
+      <c r="E1965">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="F1965">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1966" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1966">
+        <v>46.19890909090909</v>
+      </c>
+      <c r="D1966">
+        <v>165</v>
+      </c>
+      <c r="E1966">
+        <v>24.360246913580252</v>
+      </c>
+      <c r="F1966">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1967" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1967">
+        <v>61.25</v>
+      </c>
+      <c r="D1967">
+        <v>10</v>
+      </c>
+      <c r="E1967">
+        <v>35.83</v>
+      </c>
+      <c r="F1967">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1968" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1968">
+        <v>48.364999999999995</v>
+      </c>
+      <c r="D1968">
+        <v>82</v>
+      </c>
+      <c r="E1968">
+        <v>37.651898734177216</v>
+      </c>
+      <c r="F1968">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1969" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1969">
+        <v>53.48</v>
+      </c>
+      <c r="D1969">
+        <v>100</v>
+      </c>
+      <c r="E1969">
+        <v>32.309200000000004</v>
+      </c>
+      <c r="F1969">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1970" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1970">
+        <v>38.579338842975211</v>
+      </c>
+      <c r="D1970">
+        <v>121</v>
+      </c>
+      <c r="E1970">
+        <v>16.855454545454545</v>
+      </c>
+      <c r="F1970">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1971" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1971">
+        <v>45</v>
+      </c>
+      <c r="D1971">
+        <v>24</v>
+      </c>
+      <c r="E1971">
+        <v>27.83</v>
+      </c>
+      <c r="F1971">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1972" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1972">
+        <v>53.82</v>
+      </c>
+      <c r="D1972">
+        <v>33</v>
+      </c>
+      <c r="E1972">
+        <v>21</v>
+      </c>
+      <c r="F1972">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1973" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1973">
+        <v>30.156470588235294</v>
+      </c>
+      <c r="D1973">
+        <v>51</v>
+      </c>
+      <c r="E1973">
+        <v>13.5298</v>
+      </c>
+      <c r="F1973">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1974" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1974">
+        <v>31.63</v>
+      </c>
+      <c r="D1974">
+        <v>35</v>
+      </c>
+      <c r="E1974">
+        <v>19.46</v>
+      </c>
+      <c r="F1974">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1975" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1975">
+        <v>41.817462686567161</v>
+      </c>
+      <c r="D1975">
+        <v>134</v>
+      </c>
+      <c r="E1975">
+        <v>22.129849624060149</v>
+      </c>
+      <c r="F1975">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1976" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1976">
+        <v>21.615925925925925</v>
+      </c>
+      <c r="D1976">
+        <v>27</v>
+      </c>
+      <c r="E1976">
+        <v>13.531851851851853</v>
+      </c>
+      <c r="F1976">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1977" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1977">
+        <v>39.625851063829785</v>
+      </c>
+      <c r="D1977">
+        <v>94</v>
+      </c>
+      <c r="E1977">
+        <v>21.978191489361699</v>
+      </c>
+      <c r="F1977">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1978" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1978">
+        <v>46.59</v>
+      </c>
+      <c r="D1978">
+        <v>35</v>
+      </c>
+      <c r="E1978">
+        <v>22.96</v>
+      </c>
+      <c r="F1978">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1979" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1979">
+        <v>49.25</v>
+      </c>
+      <c r="D1979">
+        <v>12</v>
+      </c>
+      <c r="E1979">
+        <v>31.73</v>
+      </c>
+      <c r="F1979">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1980" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1980">
+        <v>45.367623931623925</v>
+      </c>
+      <c r="D1980">
+        <v>585</v>
+      </c>
+      <c r="E1980">
+        <v>29.613807890222983</v>
+      </c>
+      <c r="F1980">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1981" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1981">
+        <v>51.345108695652172</v>
+      </c>
+      <c r="D1981">
+        <v>368</v>
+      </c>
+      <c r="E1981">
+        <v>33.296538461538468</v>
+      </c>
+      <c r="F1981">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1982" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1982">
+        <v>42.205806451612908</v>
+      </c>
+      <c r="D1982">
+        <v>93</v>
+      </c>
+      <c r="E1982">
+        <v>20.053932584269663</v>
+      </c>
+      <c r="F1982">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1983" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1983">
+        <v>23.717333333333332</v>
+      </c>
+      <c r="D1983">
+        <v>30</v>
+      </c>
+      <c r="E1983">
+        <v>12.617142857142856</v>
+      </c>
+      <c r="F1983">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1984" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1984">
+        <v>34.159999999999997</v>
+      </c>
+      <c r="D1984">
+        <v>16</v>
+      </c>
+      <c r="E1984">
+        <v>27.359999999999996</v>
+      </c>
+      <c r="F1984">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1985" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1985">
+        <v>54.15768707482993</v>
+      </c>
+      <c r="D1985">
+        <v>294</v>
+      </c>
+      <c r="E1985">
+        <v>36.051748251748251</v>
+      </c>
+      <c r="F1985">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1986" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1986">
+        <v>39.277380952380952</v>
+      </c>
+      <c r="D1986">
+        <v>42</v>
+      </c>
+      <c r="E1986">
+        <v>23.777441860465114</v>
+      </c>
+      <c r="F1986">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1987" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1987">
+        <v>44.095058823529413</v>
+      </c>
+      <c r="D1987">
+        <v>170</v>
+      </c>
+      <c r="E1987">
+        <v>21.981395348837207</v>
+      </c>
+      <c r="F1987">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1988" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1988">
+        <v>23.626241610738255</v>
+      </c>
+      <c r="D1988">
+        <v>149</v>
+      </c>
+      <c r="E1988">
+        <v>17.531438356164383</v>
+      </c>
+      <c r="F1988">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1989" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1989">
+        <v>60.330000000000005</v>
+      </c>
+      <c r="D1989">
+        <v>9</v>
+      </c>
+      <c r="E1989">
+        <v>21.25</v>
+      </c>
+      <c r="F1989">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1990" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1990">
+        <v>35.375999999999998</v>
+      </c>
+      <c r="D1990">
+        <v>70</v>
+      </c>
+      <c r="E1990">
+        <v>26.294615384615383</v>
+      </c>
+      <c r="F1990">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1991" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1991">
+        <v>43.128571428571426</v>
+      </c>
+      <c r="D1991">
+        <v>56</v>
+      </c>
+      <c r="E1991">
+        <v>24.042321428571427</v>
+      </c>
+      <c r="F1991">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1992" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1992">
+        <v>57.055645161290322</v>
+      </c>
+      <c r="D1992">
+        <v>62</v>
+      </c>
+      <c r="E1992">
+        <v>32.150645161290321</v>
+      </c>
+      <c r="F1992">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1993" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1993">
+        <v>15</v>
+      </c>
+      <c r="D1993">
+        <v>4</v>
+      </c>
+      <c r="E1993">
+        <v>11.25</v>
+      </c>
+      <c r="F1993">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1994" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1994">
+        <v>28.5</v>
+      </c>
+      <c r="D1994">
+        <v>1</v>
+      </c>
+      <c r="E1994">
+        <v>10</v>
+      </c>
+      <c r="F1994">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1995" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1995">
+        <v>23.83</v>
+      </c>
+      <c r="D1995">
+        <v>12</v>
+      </c>
+      <c r="E1995">
+        <v>9.44</v>
+      </c>
+      <c r="F1995">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1996" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1996">
+        <v>45.437025641025635</v>
+      </c>
+      <c r="D1996">
+        <v>195</v>
+      </c>
+      <c r="E1996">
+        <v>28.144923076923078</v>
+      </c>
+      <c r="F1996">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1997" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1997">
+        <v>31.7075</v>
+      </c>
+      <c r="D1997">
+        <v>24</v>
+      </c>
+      <c r="E1997">
+        <v>12.263043478260871</v>
+      </c>
+      <c r="F1997">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1998" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1998">
+        <v>46.148918918918916</v>
+      </c>
+      <c r="D1998">
+        <v>111</v>
+      </c>
+      <c r="E1998">
+        <v>27.078971962616819</v>
+      </c>
+      <c r="F1998">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1999" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1999">
+        <v>43.820277777777775</v>
+      </c>
+      <c r="D1999">
+        <v>36</v>
+      </c>
+      <c r="E1999">
+        <v>21.094736842105263</v>
+      </c>
+      <c r="F1999">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2000" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2000">
+        <v>41.967741935483872</v>
+      </c>
+      <c r="D2000">
+        <v>31</v>
+      </c>
+      <c r="E2000">
+        <v>20.651999999999997</v>
+      </c>
+      <c r="F2000">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2001" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2001">
+        <v>51.29</v>
+      </c>
+      <c r="D2001">
+        <v>7</v>
+      </c>
+      <c r="E2001">
+        <v>23.109999999999996</v>
+      </c>
+      <c r="F2001">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2002" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2002">
+        <v>45.306842105263158</v>
+      </c>
+      <c r="D2002">
+        <v>76</v>
+      </c>
+      <c r="E2002">
+        <v>29.992597402597408</v>
+      </c>
+      <c r="F2002">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2003" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2003">
+        <v>55.373638676844784</v>
+      </c>
+      <c r="D2003">
+        <v>393</v>
+      </c>
+      <c r="E2003">
+        <v>29.791898734177213</v>
+      </c>
+      <c r="F2003">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2004" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2004">
+        <v>23.197575757575756</v>
+      </c>
+      <c r="D2004">
+        <v>66</v>
+      </c>
+      <c r="E2004">
+        <v>14.171846153846156</v>
+      </c>
+      <c r="F2004">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2005" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2005">
+        <v>19.46</v>
+      </c>
+      <c r="D2005">
+        <v>13</v>
+      </c>
+      <c r="E2005">
+        <v>24.9</v>
+      </c>
+      <c r="F2005">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2006" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2006">
+        <v>65.87</v>
+      </c>
+      <c r="D2006">
+        <v>15</v>
+      </c>
+      <c r="E2006">
+        <v>65.62</v>
+      </c>
+      <c r="F2006">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2007" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2007">
+        <v>52.669438943894392</v>
+      </c>
+      <c r="D2007">
+        <v>303</v>
+      </c>
+      <c r="E2007">
+        <v>37.131914191419142</v>
+      </c>
+      <c r="F2007">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2008" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2008" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2008">
+        <v>21.660714285714285</v>
+      </c>
+      <c r="D2008">
+        <v>56</v>
+      </c>
+      <c r="E2008">
+        <v>17.985090909090907</v>
+      </c>
+      <c r="F2008">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2009" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2009" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2009">
+        <v>23.52</v>
+      </c>
+      <c r="D2009">
+        <v>33</v>
+      </c>
+      <c r="E2009">
+        <v>14.03</v>
+      </c>
+      <c r="F2009">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2010" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2010" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2010">
+        <v>34.860689655172408</v>
+      </c>
+      <c r="D2010">
+        <v>29</v>
+      </c>
+      <c r="E2010">
+        <v>19.890344827586208</v>
+      </c>
+      <c r="F2010">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2011" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2011" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2011">
+        <v>34.244285714285716</v>
+      </c>
+      <c r="D2011">
+        <v>203</v>
+      </c>
+      <c r="E2011">
+        <v>24.089802955665029</v>
+      </c>
+      <c r="F2011">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2012" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2012" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2012">
+        <v>32.212164948453605</v>
+      </c>
+      <c r="D2012">
+        <v>97</v>
+      </c>
+      <c r="E2012">
+        <v>17.977096774193548</v>
+      </c>
+      <c r="F2012">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2013" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2013" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2013">
+        <v>28.83</v>
+      </c>
+      <c r="D2013">
+        <v>6</v>
+      </c>
+      <c r="E2013">
+        <v>21.17</v>
+      </c>
+      <c r="F2013">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2014" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2014" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2014">
+        <v>38.371981132075476</v>
+      </c>
+      <c r="D2014">
+        <v>106</v>
+      </c>
+      <c r="E2014">
+        <v>29.444299065420559</v>
+      </c>
+      <c r="F2014">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2015" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2015" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2015">
+        <v>42.065333333333335</v>
+      </c>
+      <c r="D2015">
+        <v>30</v>
+      </c>
+      <c r="E2015">
+        <v>25.139000000000003</v>
+      </c>
+      <c r="F2015">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2016" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2016" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2016">
+        <v>23</v>
+      </c>
+      <c r="D2016">
+        <v>3</v>
+      </c>
+      <c r="E2016">
+        <v>5.5</v>
+      </c>
+      <c r="F2016">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2017" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2017" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2017">
+        <v>37.776428571428575</v>
+      </c>
+      <c r="D2017">
+        <v>56</v>
+      </c>
+      <c r="E2017">
+        <v>16.829629629629629</v>
+      </c>
+      <c r="F2017">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2018" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2018" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2018">
+        <v>22.997912087912088</v>
+      </c>
+      <c r="D2018">
+        <v>91</v>
+      </c>
+      <c r="E2018">
+        <v>17.022183908045974</v>
+      </c>
+      <c r="F2018">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2019" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2019">
+        <v>45.606363636363646</v>
+      </c>
+      <c r="D2019">
+        <v>121</v>
+      </c>
+      <c r="E2019">
+        <v>21.524117647058823</v>
+      </c>
+      <c r="F2019">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2020" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2020" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2020">
+        <v>52.874643765903322</v>
+      </c>
+      <c r="D2020">
+        <v>786</v>
+      </c>
+      <c r="E2020">
+        <v>34.788399487836102</v>
+      </c>
+      <c r="F2020">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2021" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2021" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2021">
+        <v>51.78</v>
+      </c>
+      <c r="D2021">
+        <v>148</v>
+      </c>
+      <c r="E2021">
+        <v>27.034200000000002</v>
+      </c>
+      <c r="F2021">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2022" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2022" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2022">
+        <v>57.339399141630906</v>
+      </c>
+      <c r="D2022">
+        <v>699</v>
+      </c>
+      <c r="E2022">
+        <v>34.835771428571427</v>
+      </c>
+      <c r="F2022">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2023" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2023" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2023">
+        <v>25.71</v>
+      </c>
+      <c r="D2023">
+        <v>19</v>
+      </c>
+      <c r="E2023">
+        <v>9.51</v>
+      </c>
+      <c r="F2023">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2024" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2024">
+        <v>45.344810426540292</v>
+      </c>
+      <c r="D2024">
+        <v>422</v>
+      </c>
+      <c r="E2024">
+        <v>29.163206650831359</v>
+      </c>
+      <c r="F2024">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2025" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2025" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2025">
+        <v>47.858888888888892</v>
+      </c>
+      <c r="D2025">
+        <v>126</v>
+      </c>
+      <c r="E2025">
+        <v>34.372800000000005</v>
+      </c>
+      <c r="F2025">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2026" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2026" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2026">
+        <v>56.47</v>
+      </c>
+      <c r="D2026">
+        <v>51</v>
+      </c>
+      <c r="E2026">
+        <v>37.31</v>
+      </c>
+      <c r="F2026">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2027" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2027">
+        <v>55.218794326241131</v>
+      </c>
+      <c r="D2027">
+        <v>987</v>
+      </c>
+      <c r="E2027">
+        <v>34.942487257900105</v>
+      </c>
+      <c r="F2027">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2028" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2028">
+        <v>61.882879870129848</v>
+      </c>
+      <c r="D2028">
+        <v>3080</v>
+      </c>
+      <c r="E2028">
+        <v>45.460100747481306</v>
+      </c>
+      <c r="F2028">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2029" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2029">
+        <v>34.212328767123289</v>
+      </c>
+      <c r="D2029">
+        <v>73</v>
+      </c>
+      <c r="E2029">
+        <v>18.118783783783783</v>
+      </c>
+      <c r="F2029">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2030" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2030" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2030">
+        <v>47.805592417061611</v>
+      </c>
+      <c r="D2030">
+        <v>211</v>
+      </c>
+      <c r="E2030">
+        <v>32.29452380952381</v>
+      </c>
+      <c r="F2030">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2031" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2031" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2031">
+        <v>49.00848684210527</v>
+      </c>
+      <c r="D2031">
+        <v>152</v>
+      </c>
+      <c r="E2031">
+        <v>29.647039473684206</v>
+      </c>
+      <c r="F2031">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2032" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2032" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2032">
+        <v>34.41185185185185</v>
+      </c>
+      <c r="D2032">
+        <v>27</v>
+      </c>
+      <c r="E2032">
+        <v>22.411153846153844</v>
+      </c>
+      <c r="F2032">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2033" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2033" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2033">
+        <v>47.95378048780487</v>
+      </c>
+      <c r="D2033">
+        <v>82</v>
+      </c>
+      <c r="E2033">
+        <v>29.924268292682925</v>
+      </c>
+      <c r="F2033">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2034" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2034" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2034">
+        <v>45.390769230769237</v>
+      </c>
+      <c r="D2034">
+        <v>52</v>
+      </c>
+      <c r="E2034">
+        <v>29.661764705882351</v>
+      </c>
+      <c r="F2034">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2035" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2035" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2035">
+        <v>41.219207317073177</v>
+      </c>
+      <c r="D2035">
+        <v>164</v>
+      </c>
+      <c r="E2035">
+        <v>25.542407407407406</v>
+      </c>
+      <c r="F2035">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2036" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2036" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2036">
+        <v>42.007352941176471</v>
+      </c>
+      <c r="D2036">
+        <v>204</v>
+      </c>
+      <c r="E2036">
+        <v>23.188872549019607</v>
+      </c>
+      <c r="F2036">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2037" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2037" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2037">
+        <v>42.705952380952382</v>
+      </c>
+      <c r="D2037">
+        <v>126</v>
+      </c>
+      <c r="E2037">
+        <v>21.113599999999998</v>
+      </c>
+      <c r="F2037">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2038" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2038">
+        <v>46.8938202247191</v>
+      </c>
+      <c r="D2038">
+        <v>89</v>
+      </c>
+      <c r="E2038">
+        <v>23.789662921348313</v>
+      </c>
+      <c r="F2038">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2039" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2039" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2039">
+        <v>50.451082949308763</v>
+      </c>
+      <c r="D2039">
+        <v>434</v>
+      </c>
+      <c r="E2039">
+        <v>28.500619266055047</v>
+      </c>
+      <c r="F2039">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2040" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2040" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2040">
+        <v>52.776777777777774</v>
+      </c>
+      <c r="D2040">
+        <v>180</v>
+      </c>
+      <c r="E2040">
+        <v>31.867333333333331</v>
+      </c>
+      <c r="F2040">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2041" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2041" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2041">
+        <v>42.231171875000001</v>
+      </c>
+      <c r="D2041">
+        <v>128</v>
+      </c>
+      <c r="E2041">
+        <v>23.460708661417325</v>
+      </c>
+      <c r="F2041">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2042" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2042" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2042">
+        <v>52.439223300970873</v>
+      </c>
+      <c r="D2042">
+        <v>206</v>
+      </c>
+      <c r="E2042">
+        <v>35.285247524752478</v>
+      </c>
+      <c r="F2042">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2043" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2043" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2043">
+        <v>54.27</v>
+      </c>
+      <c r="D2043">
+        <v>11</v>
+      </c>
+      <c r="E2043">
+        <v>31.019999999999996</v>
+      </c>
+      <c r="F2043">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2044" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2044" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2044">
+        <v>55.010956937799044</v>
+      </c>
+      <c r="D2044">
+        <v>209</v>
+      </c>
+      <c r="E2044">
+        <v>36.204407582938387</v>
+      </c>
+      <c r="F2044">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2045" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2045" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2045">
+        <v>44.205384615384617</v>
+      </c>
+      <c r="D2045">
+        <v>39</v>
+      </c>
+      <c r="E2045">
+        <v>33.758499999999998</v>
+      </c>
+      <c r="F2045">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2046" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2046" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2046">
+        <v>53.295757575757577</v>
+      </c>
+      <c r="D2046">
+        <v>66</v>
+      </c>
+      <c r="E2046">
+        <v>34.379696969696965</v>
+      </c>
+      <c r="F2046">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2047" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2047" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2047">
+        <v>43.314114583333328</v>
+      </c>
+      <c r="D2047">
+        <v>192</v>
+      </c>
+      <c r="E2047">
+        <v>38.555885416666662</v>
+      </c>
+      <c r="F2047">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2048" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2048" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2048">
+        <v>40.0824</v>
+      </c>
+      <c r="D2048">
+        <v>25</v>
+      </c>
+      <c r="E2048">
+        <v>13.752173913043478</v>
+      </c>
+      <c r="F2048">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2049" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2049" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2049">
+        <v>59.948724534986717</v>
+      </c>
+      <c r="D2049">
+        <v>1129</v>
+      </c>
+      <c r="E2049">
+        <v>41.662375886524821</v>
+      </c>
+      <c r="F2049">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2050" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2050">
+        <v>29.900983606557379</v>
+      </c>
+      <c r="D2050">
+        <v>122</v>
+      </c>
+      <c r="E2050">
+        <v>16.400749999999999</v>
+      </c>
+      <c r="F2050">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2051" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2051" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2051">
+        <v>45.980632911392405</v>
+      </c>
+      <c r="D2051">
+        <v>316</v>
+      </c>
+      <c r="E2051">
+        <v>26.62329073482428</v>
+      </c>
+      <c r="F2051">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2052" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2052" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2052">
+        <v>34.250681818181818</v>
+      </c>
+      <c r="D2052">
+        <v>44</v>
+      </c>
+      <c r="E2052">
+        <v>27.685227272727275</v>
+      </c>
+      <c r="F2052">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2053" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2053" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2053">
+        <v>58.031630769230766</v>
+      </c>
+      <c r="D2053">
+        <v>325</v>
+      </c>
+      <c r="E2053">
+        <v>37.316281249999996</v>
+      </c>
+      <c r="F2053">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2054" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2054">
+        <v>50.7</v>
+      </c>
+      <c r="D2054">
+        <v>50</v>
+      </c>
+      <c r="E2054">
+        <v>40.65</v>
+      </c>
+      <c r="F2054">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2055" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2055">
+        <v>52.392871287128706</v>
+      </c>
+      <c r="D2055">
+        <v>101</v>
+      </c>
+      <c r="E2055">
+        <v>37.272178217821782</v>
+      </c>
+      <c r="F2055">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2056" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2056">
+        <v>49.389230769230771</v>
+      </c>
+      <c r="D2056">
+        <v>182</v>
+      </c>
+      <c r="E2056">
+        <v>36.969835164835168</v>
+      </c>
+      <c r="F2056">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2057" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2057">
+        <v>52.552888888888894</v>
+      </c>
+      <c r="D2057">
+        <v>180</v>
+      </c>
+      <c r="E2057">
+        <v>36.127722222222218</v>
+      </c>
+      <c r="F2057">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2058" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2058">
+        <v>54.958453608247424</v>
+      </c>
+      <c r="D2058">
+        <v>97</v>
+      </c>
+      <c r="E2058">
+        <v>27.443608247422681</v>
+      </c>
+      <c r="F2058">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2059" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2059">
+        <v>51.715627906976735</v>
+      </c>
+      <c r="D2059">
+        <v>215</v>
+      </c>
+      <c r="E2059">
+        <v>30.710327102803738</v>
+      </c>
+      <c r="F2059">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2060" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2060">
+        <v>56.763499999999993</v>
+      </c>
+      <c r="D2060">
+        <v>260</v>
+      </c>
+      <c r="E2060">
+        <v>31.298030888030887</v>
+      </c>
+      <c r="F2060">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2061" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2061">
+        <v>18.1312</v>
+      </c>
+      <c r="D2061">
+        <v>50</v>
+      </c>
+      <c r="E2061">
+        <v>13.476923076923079</v>
+      </c>
+      <c r="F2061">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2062" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2062">
+        <v>45.881294117647066</v>
+      </c>
+      <c r="D2062">
+        <v>85</v>
+      </c>
+      <c r="E2062">
+        <v>27.284166666666664</v>
+      </c>
+      <c r="F2062">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2063" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2063">
+        <v>39.751999999999995</v>
+      </c>
+      <c r="D2063">
+        <v>30</v>
+      </c>
+      <c r="E2063">
+        <v>36.259354838709676</v>
+      </c>
+      <c r="F2063">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2064" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2064">
+        <v>44.223753976670196</v>
+      </c>
+      <c r="D2064">
+        <v>943</v>
+      </c>
+      <c r="E2064">
+        <v>27.251019108280254</v>
+      </c>
+      <c r="F2064">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2065" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2065">
+        <v>48.621864406779672</v>
+      </c>
+      <c r="D2065">
+        <v>59</v>
+      </c>
+      <c r="E2065">
+        <v>31.728965517241377</v>
+      </c>
+      <c r="F2065">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2066" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2066">
+        <v>25.085714285714282</v>
+      </c>
+      <c r="D2066">
+        <v>42</v>
+      </c>
+      <c r="E2066">
+        <v>15.043902439024389</v>
+      </c>
+      <c r="F2066">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2067" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2067">
+        <v>60.451072796934866</v>
+      </c>
+      <c r="D2067">
+        <v>261</v>
+      </c>
+      <c r="E2067">
+        <v>38.131000000000007</v>
+      </c>
+      <c r="F2067">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2068" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2068">
+        <v>35.498000000000005</v>
+      </c>
+      <c r="D2068">
+        <v>30</v>
+      </c>
+      <c r="E2068">
+        <v>20.294666666666668</v>
+      </c>
+      <c r="F2068">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2069" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2069">
+        <v>43.534117647058828</v>
+      </c>
+      <c r="D2069">
+        <v>68</v>
+      </c>
+      <c r="E2069">
+        <v>26.494999999999997</v>
+      </c>
+      <c r="F2069">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2070" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2070">
+        <v>43.02</v>
+      </c>
+      <c r="D2070">
+        <v>66</v>
+      </c>
+      <c r="E2070">
+        <v>15.88</v>
+      </c>
+      <c r="F2070">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2071" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2071" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2071">
+        <v>32.341470588235296</v>
+      </c>
+      <c r="D2071">
+        <v>102</v>
+      </c>
+      <c r="E2071">
+        <v>16.173076923076923</v>
+      </c>
+      <c r="F2071">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2072" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2072">
+        <v>45.416800000000002</v>
+      </c>
+      <c r="D2072">
+        <v>125</v>
+      </c>
+      <c r="E2072">
+        <v>27.404400000000003</v>
+      </c>
+      <c r="F2072">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2073" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2073">
+        <v>42.643157894736845</v>
+      </c>
+      <c r="D2073">
+        <v>38</v>
+      </c>
+      <c r="E2073">
+        <v>26.11783783783784</v>
+      </c>
+      <c r="F2073">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2074" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2074" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2074">
+        <v>60.875034642032332</v>
+      </c>
+      <c r="D2074">
+        <v>1299</v>
+      </c>
+      <c r="E2074">
+        <v>43.67147149460709</v>
+      </c>
+      <c r="F2074">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2075" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2075" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2075">
+        <v>68.057987964416526</v>
+      </c>
+      <c r="D2075">
+        <v>11466</v>
+      </c>
+      <c r="E2075">
+        <v>52.372837932238902</v>
+      </c>
+      <c r="F2075">
+        <v>11452</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2076" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2076" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2076">
+        <v>29.797727272727272</v>
+      </c>
+      <c r="D2076">
+        <v>88</v>
+      </c>
+      <c r="E2076">
+        <v>12.784831460674157</v>
+      </c>
+      <c r="F2076">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2077" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2077" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2077">
+        <v>45.067625000000007</v>
+      </c>
+      <c r="D2077">
+        <v>80</v>
+      </c>
+      <c r="E2077">
+        <v>38.863164556962019</v>
+      </c>
+      <c r="F2077">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2078" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2078" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2078">
+        <v>44.11</v>
+      </c>
+      <c r="D2078">
+        <v>14</v>
+      </c>
+      <c r="E2078">
+        <v>13.55</v>
+      </c>
+      <c r="F2078">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2079" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2079">
+        <v>10.91</v>
+      </c>
+      <c r="D2079">
+        <v>37</v>
+      </c>
+      <c r="E2079">
+        <v>8.42</v>
+      </c>
+      <c r="F2079">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2080" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2080">
+        <v>32.864042553191489</v>
+      </c>
+      <c r="D2080">
+        <v>47</v>
+      </c>
+      <c r="E2080">
+        <v>18.075555555555557</v>
+      </c>
+      <c r="F2080">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2081" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2081">
+        <v>34.458148148148148</v>
+      </c>
+      <c r="D2081">
+        <v>81</v>
+      </c>
+      <c r="E2081">
+        <v>27.097283950617278</v>
+      </c>
+      <c r="F2081">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2082" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2082">
+        <v>34.17</v>
+      </c>
+      <c r="D2082">
+        <v>9</v>
+      </c>
+      <c r="E2082">
+        <v>12.5</v>
+      </c>
+      <c r="F2082">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2083" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2083">
+        <v>33.9</v>
+      </c>
+      <c r="D2083">
+        <v>49</v>
+      </c>
+      <c r="E2083">
+        <v>14.99</v>
+      </c>
+      <c r="F2083">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2084" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2084">
+        <v>36.620243902439022</v>
+      </c>
+      <c r="D2084">
+        <v>41</v>
+      </c>
+      <c r="E2084">
+        <v>21.661999999999999</v>
+      </c>
+      <c r="F2084">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2085" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2085">
+        <v>33.861956521739131</v>
+      </c>
+      <c r="D2085">
+        <v>92</v>
+      </c>
+      <c r="E2085">
+        <v>19.620212765957447</v>
+      </c>
+      <c r="F2085">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2086" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2086">
+        <v>28.555978260869566</v>
+      </c>
+      <c r="D2086">
+        <v>92</v>
+      </c>
+      <c r="E2086">
+        <v>16.846559139784947</v>
+      </c>
+      <c r="F2086">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2087" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2087">
+        <v>45.079469696969696</v>
+      </c>
+      <c r="D2087">
+        <v>132</v>
+      </c>
+      <c r="E2087">
+        <v>36.280846153846156</v>
+      </c>
+      <c r="F2087">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2088" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2088">
+        <v>39.269310344827588</v>
+      </c>
+      <c r="D2088">
+        <v>58</v>
+      </c>
+      <c r="E2088">
+        <v>43.985892857142858</v>
+      </c>
+      <c r="F2088">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2089" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2089">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D2089">
+        <v>5</v>
+      </c>
+      <c r="E2089">
+        <v>7.2</v>
+      </c>
+      <c r="F2089">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2090" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2090">
+        <v>59.95698863636364</v>
+      </c>
+      <c r="D2090">
+        <v>176</v>
+      </c>
+      <c r="E2090">
+        <v>31.948181818181819</v>
+      </c>
+      <c r="F2090">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2091" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2091">
+        <v>43.669999999999995</v>
+      </c>
+      <c r="D2091">
+        <v>24</v>
+      </c>
+      <c r="E2091">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="F2091">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2092" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2092">
+        <v>59.163620689655168</v>
+      </c>
+      <c r="D2092">
+        <v>58</v>
+      </c>
+      <c r="E2092">
+        <v>31.326842105263161</v>
+      </c>
+      <c r="F2092">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2093" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2093">
+        <v>35.139600000000002</v>
+      </c>
+      <c r="D2093">
+        <v>100</v>
+      </c>
+      <c r="E2093">
+        <v>30.098269230769233</v>
+      </c>
+      <c r="F2093">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2094" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2094">
+        <v>48.777763157894732</v>
+      </c>
+      <c r="D2094">
+        <v>76</v>
+      </c>
+      <c r="E2094">
+        <v>26.225897435897433</v>
+      </c>
+      <c r="F2094">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2095" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2095">
+        <v>50.550366379310347</v>
+      </c>
+      <c r="D2095">
+        <v>464</v>
+      </c>
+      <c r="E2095">
+        <v>36.542548596112304</v>
+      </c>
+      <c r="F2095">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2096" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2096">
+        <v>32.242926829268292</v>
+      </c>
+      <c r="D2096">
+        <v>41</v>
+      </c>
+      <c r="E2096">
+        <v>24.031428571428574</v>
+      </c>
+      <c r="F2096">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2097" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2097">
+        <v>50.324264705882356</v>
+      </c>
+      <c r="D2097">
+        <v>68</v>
+      </c>
+      <c r="E2097">
+        <v>26.718823529411765</v>
+      </c>
+      <c r="F2097">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2098" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2098">
+        <v>39.427142857142861</v>
+      </c>
+      <c r="D2098">
+        <v>21</v>
+      </c>
+      <c r="E2098">
+        <v>18.630526315789474</v>
+      </c>
+      <c r="F2098">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2099" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2099">
+        <v>40.622574257425747</v>
+      </c>
+      <c r="D2099">
+        <v>202</v>
+      </c>
+      <c r="E2099">
+        <v>28.40926470588235</v>
+      </c>
+      <c r="F2099">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2100" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2100">
+        <v>55.644340136054424</v>
+      </c>
+      <c r="D2100">
+        <v>735</v>
+      </c>
+      <c r="E2100">
+        <v>37.723106267029976</v>
+      </c>
+      <c r="F2100">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2101" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2101">
+        <v>38.327391304347827</v>
+      </c>
+      <c r="D2101">
+        <v>69</v>
+      </c>
+      <c r="E2101">
+        <v>23.020735294117646</v>
+      </c>
+      <c r="F2101">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2102" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2102">
+        <v>33.21</v>
+      </c>
+      <c r="D2102">
+        <v>17</v>
+      </c>
+      <c r="E2102">
+        <v>29.64</v>
+      </c>
+      <c r="F2102">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2103" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2103">
+        <v>46.434666666666665</v>
+      </c>
+      <c r="D2103">
+        <v>15</v>
+      </c>
+      <c r="E2103">
+        <v>17.095384615384617</v>
+      </c>
+      <c r="F2103">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2104" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2104">
+        <v>53.560285714285712</v>
+      </c>
+      <c r="D2104">
+        <v>70</v>
+      </c>
+      <c r="E2104">
+        <v>24.553913043478261</v>
+      </c>
+      <c r="F2104">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2105" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2105">
+        <v>35.123125000000002</v>
+      </c>
+      <c r="D2105">
+        <v>16</v>
+      </c>
+      <c r="E2105">
+        <v>12.876875</v>
+      </c>
+      <c r="F2105">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2106" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2106">
+        <v>53.94</v>
+      </c>
+      <c r="D2106">
+        <v>9</v>
+      </c>
+      <c r="E2106">
+        <v>25.42</v>
+      </c>
+      <c r="F2106">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2107" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2107">
+        <v>60.83</v>
+      </c>
+      <c r="D2107">
+        <v>20</v>
+      </c>
+      <c r="E2107">
+        <v>44.21</v>
+      </c>
+      <c r="F2107">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2108" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2108">
+        <v>53.938709677419354</v>
+      </c>
+      <c r="D2108">
+        <v>31</v>
+      </c>
+      <c r="E2108">
+        <v>31.981666666666666</v>
+      </c>
+      <c r="F2108">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2109" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2109">
+        <v>40.608546511627907</v>
+      </c>
+      <c r="D2109">
+        <v>172</v>
+      </c>
+      <c r="E2109">
+        <v>25.881918604651165</v>
+      </c>
+      <c r="F2109">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2110" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2110">
+        <v>37.205799999999996</v>
+      </c>
+      <c r="D2110">
+        <v>50</v>
+      </c>
+      <c r="E2110">
+        <v>29.817599999999999</v>
+      </c>
+      <c r="F2110">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2111" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2111">
+        <v>50.31</v>
+      </c>
+      <c r="D2111">
+        <v>8</v>
+      </c>
+      <c r="E2111">
+        <v>21.72</v>
+      </c>
+      <c r="F2111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2112" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2112">
+        <v>38.463250000000002</v>
+      </c>
+      <c r="D2112">
+        <v>160</v>
+      </c>
+      <c r="E2112">
+        <v>28.956149068322979</v>
+      </c>
+      <c r="F2112">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2113" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2113">
+        <v>35.206666666666671</v>
+      </c>
+      <c r="D2113">
+        <v>12</v>
+      </c>
+      <c r="E2113">
+        <v>22.393333333333334</v>
+      </c>
+      <c r="F2113">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2114" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2114">
+        <v>8.83</v>
+      </c>
+      <c r="D2114">
+        <v>6</v>
+      </c>
+      <c r="E2114">
+        <v>10.6</v>
+      </c>
+      <c r="F2114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2115" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2115">
+        <v>45.091428571428573</v>
+      </c>
+      <c r="D2115">
+        <v>28</v>
+      </c>
+      <c r="E2115">
+        <v>23.328571428571429</v>
+      </c>
+      <c r="F2115">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2116" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2116">
+        <v>54.309657142857134</v>
+      </c>
+      <c r="D2116">
+        <v>700</v>
+      </c>
+      <c r="E2116">
+        <v>33.144793152639089</v>
+      </c>
+      <c r="F2116">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2117" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2117">
+        <v>37.485479452054797</v>
+      </c>
+      <c r="D2117">
+        <v>73</v>
+      </c>
+      <c r="E2117">
+        <v>40.89</v>
+      </c>
+      <c r="F2117">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2118" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2118">
+        <v>23.93</v>
+      </c>
+      <c r="D2118">
+        <v>15</v>
+      </c>
+      <c r="E2118">
+        <v>10.8</v>
+      </c>
+      <c r="F2118">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2119" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2119">
+        <v>47.340235294117647</v>
+      </c>
+      <c r="D2119">
+        <v>85</v>
+      </c>
+      <c r="E2119">
+        <v>35.497619047619047</v>
+      </c>
+      <c r="F2119">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2120" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2120">
+        <v>47.838592000000006</v>
+      </c>
+      <c r="D2120">
+        <v>625</v>
+      </c>
+      <c r="E2120">
+        <v>29.709133226324234</v>
+      </c>
+      <c r="F2120">
+        <v>623</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1855" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/work/data/maturi_data.xlsx
+++ b/work/data/maturi_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BorisV\My Documents\dashboard\NEEBG\work\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3442A991-8CC9-4056-8DA0-AA6A177BCC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178FE581-40CD-410D-AEC4-E3C6FF6B89F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A348621D-5ED5-4FD9-8ED4-4EAC86F7337C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4244" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4244" uniqueCount="280">
   <si>
     <t>Година</t>
   </si>
@@ -878,9 +878,6 @@
   <si>
     <t>2025-2026</t>
   </si>
-  <si>
-    <t>ГР.ДОБРИЧ</t>
-  </si>
 </sst>
 </file>
 
@@ -39570,7 +39567,7 @@
         <v>279</v>
       </c>
       <c r="B1917" t="s">
-        <v>280</v>
+        <v>68</v>
       </c>
       <c r="C1917">
         <v>59.204564102564099</v>
@@ -39810,7 +39807,7 @@
         <v>279</v>
       </c>
       <c r="B1929" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C1929">
         <v>26.128620689655168</v>
